--- a/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="314">
   <si>
     <t>set</t>
   </si>
@@ -2341,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -2946,6 +2946,9 @@
       </c>
     </row>
     <row r="6" spans="1:69">
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>

--- a/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="315">
   <si>
     <t>set</t>
   </si>
@@ -508,6 +508,9 @@
   </si>
   <si>
     <t>PHS002</t>
+  </si>
+  <si>
+    <t>GasMinUsage</t>
   </si>
   <si>
     <t>category</t>
@@ -1430,7 +1433,7 @@
         <v>2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1472,6 +1475,9 @@
       </c>
       <c r="N4" t="s">
         <v>162</v>
+      </c>
+      <c r="O4" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2085,37 +2091,37 @@
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AE1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AI1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AS1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AZ1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
@@ -2123,211 +2129,211 @@
     </row>
     <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="R2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="S2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="T2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="W2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="X2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AB2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AE2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AH2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AI2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AJ2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AK2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AP2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AQ2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AR2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AS2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AT2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AU2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AV2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AW2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AX2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AY2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AZ2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="BA2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="BB2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="BC2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="BD2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BE2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="BF2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="BG2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BH2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BI2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BJ2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BK2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="BL2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="BM2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="BN2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BO2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="BP2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="BQ2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:69">
@@ -2753,7 +2759,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -3170,228 +3176,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AK1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AV1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BM1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="V2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="X2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AB2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AC2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AD2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AE2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AF2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AH2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AI2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AJ2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AK2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AR2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AS2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AT2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AU2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AV2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AW2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AX2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AY2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AZ2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="BA2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="BB2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="BC2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="BD2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BE2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BF2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BG2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="BH2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="BI2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="BJ2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="BK2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="BL2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="BM2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BN2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -3865,7 +3871,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>

--- a/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="327">
   <si>
     <t>set</t>
   </si>
@@ -510,7 +510,40 @@
     <t>PHS002</t>
   </si>
   <si>
-    <t>GasMinUsage</t>
+    <t>GasInfraPrereq</t>
+  </si>
+  <si>
+    <t>DemVsWind001</t>
+  </si>
+  <si>
+    <t>DemVsWind002</t>
+  </si>
+  <si>
+    <t>DemVsWind003</t>
+  </si>
+  <si>
+    <t>DemVsWind004</t>
+  </si>
+  <si>
+    <t>DemVsWind005</t>
+  </si>
+  <si>
+    <t>DemVsWind006</t>
+  </si>
+  <si>
+    <t>DemVsWind007</t>
+  </si>
+  <si>
+    <t>DemVsWind008</t>
+  </si>
+  <si>
+    <t>DemVsWind009</t>
+  </si>
+  <si>
+    <t>DemVsWind010</t>
+  </si>
+  <si>
+    <t>DemVsSol001</t>
   </si>
   <si>
     <t>category</t>
@@ -748,6 +781,9 @@
   </si>
   <si>
     <t>UDCMultiplierTotalCapacity</t>
+  </si>
+  <si>
+    <t>UDCMultiplierDemand</t>
   </si>
   <si>
     <t>UDCTag</t>
@@ -1433,7 +1469,7 @@
         <v>2</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1511,6 +1547,9 @@
       <c r="N5" t="s">
         <v>163</v>
       </c>
+      <c r="O5" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6">
@@ -1534,6 +1573,9 @@
       <c r="L6" t="s">
         <v>163</v>
       </c>
+      <c r="O6" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7">
@@ -1554,6 +1596,9 @@
       <c r="K7" t="s">
         <v>158</v>
       </c>
+      <c r="O7" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8">
@@ -1571,6 +1616,9 @@
       <c r="K8" t="s">
         <v>159</v>
       </c>
+      <c r="O8" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9">
@@ -1588,6 +1636,9 @@
       <c r="K9" t="s">
         <v>160</v>
       </c>
+      <c r="O9" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10">
@@ -1602,6 +1653,9 @@
       <c r="E10" t="s">
         <v>141</v>
       </c>
+      <c r="O10" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11">
@@ -1616,6 +1670,9 @@
       <c r="E11" t="s">
         <v>142</v>
       </c>
+      <c r="O11" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12">
@@ -1630,6 +1687,9 @@
       <c r="E12" t="s">
         <v>143</v>
       </c>
+      <c r="O12" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13">
@@ -1644,6 +1704,9 @@
       <c r="E13" t="s">
         <v>144</v>
       </c>
+      <c r="O13" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14">
@@ -1658,6 +1721,9 @@
       <c r="E14" t="s">
         <v>145</v>
       </c>
+      <c r="O14" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15">
@@ -1671,6 +1737,9 @@
       </c>
       <c r="E15" t="s">
         <v>146</v>
+      </c>
+      <c r="O15" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -2086,257 +2155,260 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BQ8"/>
+  <dimension ref="A1:BR8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:69">
+    <row r="1" spans="1:70">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="L1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="O1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="AA1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="AE1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="AI1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="AM1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="AP1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="AS1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="AZ1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:69">
+    <row r="2" spans="1:70">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="I2" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="J2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="K2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="L2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="M2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="N2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="O2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="P2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="Q2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="R2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="S2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="T2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="U2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="V2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="W2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="X2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="Y2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="Z2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="AA2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AB2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="AC2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AD2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="AE2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="AF2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="AG2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="AH2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="AI2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AJ2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="AK2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="AL2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="AM2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="AN2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="AO2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="AP2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="AQ2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AR2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="AS2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="AT2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="AU2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="AV2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AW2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="AX2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="AY2" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="AZ2" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="BA2" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="BB2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="BC2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="BD2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="BE2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="BF2" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="BG2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="BH2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="BI2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="BJ2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="BK2" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="BL2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="BM2" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="BN2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="BO2" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="BP2" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="BQ2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="3" spans="1:69">
+        <v>255</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:70">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2542,10 +2614,13 @@
         <v>4</v>
       </c>
       <c r="BQ3">
+        <v>4</v>
+      </c>
+      <c r="BR3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:69">
+    <row r="4" spans="1:70">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -2750,8 +2825,11 @@
       <c r="BQ4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:69">
+      <c r="BR4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -2759,7 +2837,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -2948,10 +3026,13 @@
         <v>18</v>
       </c>
       <c r="BQ5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BR5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:69">
+    <row r="6" spans="1:70">
       <c r="D6" t="s">
         <v>17</v>
       </c>
@@ -3090,8 +3171,11 @@
       <c r="BP6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:69">
+      <c r="BQ6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:70">
       <c r="E7" t="s">
         <v>17</v>
       </c>
@@ -3149,8 +3233,11 @@
       <c r="BP7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:69">
+      <c r="BQ7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:70">
       <c r="V8" t="s">
         <v>17</v>
       </c>
@@ -3176,228 +3263,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="J1" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="AA1" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AK1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="AV1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="BM1" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="G2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="H2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="I2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="J2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="K2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="M2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="N2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="O2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="P2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="Q2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="R2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="S2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="T2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="U2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="V2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="W2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="X2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="Y2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="Z2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AA2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AB2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="AC2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AD2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AE2" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AF2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AH2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AI2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AJ2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="AK2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AL2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AM2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AN2" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="AO2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="AP2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AQ2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AR2" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AS2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AT2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AU2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AV2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="AW2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="AX2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AY2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AZ2" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="BA2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="BB2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="BC2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="BD2" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="BE2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="BF2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="BG2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="BH2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="BI2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="BJ2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="BK2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="BL2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="BM2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="BN2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -3871,7 +3958,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>
